--- a/data/trans_dic/P39A2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P39A2_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,66; 76,02</t>
+          <t>69,05; 76,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>65,6; 71,64</t>
+          <t>65,18; 71,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,7; 72,81</t>
+          <t>68,12; 73,05</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,78; 90,67</t>
+          <t>76,28; 90,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,71; 77,42</t>
+          <t>72,68; 77,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,55; 86,55</t>
+          <t>75,49; 85,66</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,42; 67,77</t>
+          <t>59,19; 67,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,23; 85,22</t>
+          <t>59,43; 85,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,05; 78,47</t>
+          <t>61,12; 78,08</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,5; 73,18</t>
+          <t>66,46; 73,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,84; 65,87</t>
+          <t>46,36; 65,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,11; 68,07</t>
+          <t>53,16; 67,93</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,52; 80,25</t>
+          <t>70,48; 79,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,1; 74,0</t>
+          <t>63,93; 74,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,3; 75,17</t>
+          <t>68,02; 75,06</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>386919; 428404</t>
+          <t>389145; 430528</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>386073; 421627</t>
+          <t>383622; 419079</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>779997; 838853</t>
+          <t>784765; 841620</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>841559; 1006974</t>
+          <t>847073; 1005753</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>641306; 682823</t>
+          <t>640965; 682369</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1505416; 1724565</t>
+          <t>1504211; 1706673</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>386232; 448050</t>
+          <t>391301; 449339</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>501100; 720930</t>
+          <t>502819; 721190</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>920133; 1182632</t>
+          <t>921173; 1176790</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>565092; 621873</t>
+          <t>564774; 621268</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>456034; 641314</t>
+          <t>451357; 642175</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1023195; 1241173</t>
+          <t>969249; 1238685</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2245967; 2556099</t>
+          <t>2244857; 2538854</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2109104; 2434830</t>
+          <t>2103489; 2435349</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4422301; 4867367</t>
+          <t>4404259; 4859959</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P39A2_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,78%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,05; 76,4</t>
+          <t>69,14; 76,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>65,18; 71,2</t>
+          <t>65,75; 71,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68,12; 73,05</t>
+          <t>68,27; 73,09</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,28; 90,56</t>
+          <t>74,74; 80,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,68; 77,37</t>
+          <t>71,55; 76,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,49; 85,66</t>
+          <t>74,38; 77,91</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>60,97%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59,19; 67,97</t>
+          <t>58,59; 66,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,43; 85,25</t>
+          <t>55,91; 62,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,12; 78,08</t>
+          <t>58,26; 63,53</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,46; 73,11</t>
+          <t>65,93; 72,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,36; 65,96</t>
+          <t>62,27; 67,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,16; 67,93</t>
+          <t>64,91; 69,21</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,48; 79,71</t>
+          <t>69,14; 72,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63,93; 74,02</t>
+          <t>65,86; 68,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,02; 75,06</t>
+          <t>68,01; 70,25</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>409266</t>
+          <t>440137</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>402887</t>
+          <t>435855</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>812152</t>
+          <t>875992</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>389145; 430528</t>
+          <t>417798; 460718</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>383622; 419079</t>
+          <t>416484; 455090</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>784765; 841620</t>
+          <t>844950; 904584</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>914207</t>
+          <t>738500</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>662269</t>
+          <t>732641</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1576475</t>
+          <t>1471141</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>847073; 1005753</t>
+          <t>709275; 762454</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>640965; 682369</t>
+          <t>703822; 755013</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1504211; 1706673</t>
+          <t>1437604; 1505879</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>420677</t>
+          <t>465602</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>591369</t>
+          <t>445602</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1012046</t>
+          <t>911204</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>391301; 449339</t>
+          <t>437564; 497124</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>502819; 721190</t>
+          <t>418104; 470040</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>921173; 1176790</t>
+          <t>870761; 949457</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>593645</t>
+          <t>624962</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>587425</t>
+          <t>639141</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1181070</t>
+          <t>1264103</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>564774; 621268</t>
+          <t>592898; 653212</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>451357; 642175</t>
+          <t>613028; 664858</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>969249; 1238685</t>
+          <t>1222651; 1303800</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2337794</t>
+          <t>2269200</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2243949</t>
+          <t>2253240</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4581743</t>
+          <t>4522440</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2244857; 2538854</t>
+          <t>2212180; 2321968</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2103489; 2435349</t>
+          <t>2205773; 2295612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4404259; 4859959</t>
+          <t>4453543; 4600677</t>
         </is>
       </c>
     </row>
